--- a/exports/trend_1d/TATAELXSI_full_report.xlsx
+++ b/exports/trend_1d/TATAELXSI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:U76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>14.07</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42082</v>
+        <v>42083</v>
       </c>
       <c r="H2" t="n">
-        <v>599</v>
+        <v>546</v>
       </c>
       <c r="I2" t="n">
         <v>582.1486835296241</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K2" t="n">
-        <v>60.07</v>
+        <v>45.91</v>
       </c>
       <c r="L2" t="n">
         <v>2.79</v>
@@ -555,7 +578,7 @@
         <v>1.99</v>
       </c>
       <c r="N2" t="n">
-        <v>7.74</v>
+        <v>8.85</v>
       </c>
       <c r="O2" t="n">
         <v>1.61</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>28.67</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42095</v>
+        <v>42100</v>
       </c>
       <c r="H3" t="n">
-        <v>636.48</v>
+        <v>648.03</v>
       </c>
       <c r="I3" t="n">
         <v>641.1667319133469</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>-16.57</v>
+        <v>-18.69</v>
       </c>
       <c r="L3" t="n">
-        <v>16.57</v>
+        <v>21.25</v>
       </c>
       <c r="M3" t="n">
         <v>1.26</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>18.05</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42116</v>
+        <v>42117</v>
       </c>
       <c r="H4" t="n">
-        <v>578.2</v>
+        <v>560.9</v>
       </c>
       <c r="I4" t="n">
         <v>563.478900184215</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.78</v>
+        <v>-13.45</v>
       </c>
       <c r="L4" t="n">
         <v>14.81</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>21.8</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42152</v>
+        <v>42153</v>
       </c>
       <c r="H5" t="n">
-        <v>623.9</v>
+        <v>632.5</v>
       </c>
       <c r="I5" t="n">
         <v>626.2449576173249</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K5" t="n">
-        <v>-11.23</v>
+        <v>-12.77</v>
       </c>
       <c r="L5" t="n">
         <v>15.53</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>11.52</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42157</v>
+        <v>42158</v>
       </c>
       <c r="H6" t="n">
-        <v>596.63</v>
+        <v>561.83</v>
       </c>
       <c r="I6" t="n">
         <v>567.9111343930931</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.67</v>
+        <v>-11.17</v>
       </c>
       <c r="L6" t="n">
-        <v>6.63</v>
+        <v>16.75</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.71</v>
+        <v>5.83</v>
       </c>
       <c r="O6" t="n">
         <v>1.38</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>16.27</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42198</v>
+        <v>42199</v>
       </c>
       <c r="H7" t="n">
-        <v>609.17</v>
+        <v>645.85</v>
       </c>
       <c r="I7" t="n">
         <v>629.6631244323445</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.43</v>
+        <v>-14.95</v>
       </c>
       <c r="L7" t="n">
-        <v>12.49</v>
+        <v>17.74</v>
       </c>
       <c r="M7" t="n">
         <v>1.48</v>
       </c>
       <c r="N7" t="n">
-        <v>5.51</v>
+        <v>6.02</v>
       </c>
       <c r="O7" t="n">
         <v>-5.83</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>12.72</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H8" t="n">
-        <v>1029.58</v>
+        <v>845.9</v>
       </c>
       <c r="I8" t="n">
         <v>925.5254878987348</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K8" t="n">
-        <v>59.41</v>
+        <v>30.97</v>
       </c>
       <c r="L8" t="n">
         <v>5.67</v>
       </c>
       <c r="M8" t="n">
-        <v>2.58</v>
+        <v>5.64</v>
       </c>
       <c r="N8" t="n">
-        <v>5.88</v>
+        <v>17.84</v>
       </c>
       <c r="O8" t="n">
         <v>6.02</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>33.92</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42334</v>
+        <v>42335</v>
       </c>
       <c r="H9" t="n">
-        <v>938.8</v>
+        <v>980.53</v>
       </c>
       <c r="I9" t="n">
         <v>966.6220943581305</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K9" t="n">
-        <v>-10.98</v>
+        <v>-15.92</v>
       </c>
       <c r="L9" t="n">
         <v>19.64</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>11.41</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42377</v>
+        <v>42380</v>
       </c>
       <c r="H10" t="n">
-        <v>1026.13</v>
+        <v>1012.35</v>
       </c>
       <c r="I10" t="n">
         <v>1019.017819887447</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K10" t="n">
-        <v>4.65</v>
+        <v>3.25</v>
       </c>
       <c r="L10" t="n">
         <v>7.06</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.94</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42397</v>
+        <v>42398</v>
       </c>
       <c r="H11" t="n">
-        <v>995.2</v>
+        <v>1041.3</v>
       </c>
       <c r="I11" t="n">
         <v>1006.931601596748</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
-        <v>1.69</v>
+        <v>-2.86</v>
       </c>
       <c r="L11" t="n">
-        <v>1.92</v>
+        <v>3.52</v>
       </c>
       <c r="M11" t="n">
         <v>1.76</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>16.32</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42410</v>
+        <v>42411</v>
       </c>
       <c r="H12" t="n">
-        <v>998.25</v>
+        <v>930.55</v>
       </c>
       <c r="I12" t="n">
         <v>989.1655908479197</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.13</v>
+        <v>-10.64</v>
       </c>
       <c r="L12" t="n">
-        <v>5.17</v>
+        <v>11.58</v>
       </c>
       <c r="M12" t="n">
         <v>2.2</v>
       </c>
       <c r="N12" t="n">
-        <v>6.6</v>
+        <v>6.78</v>
       </c>
       <c r="O12" t="n">
         <v>4.63</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>22.92</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42485</v>
+        <v>42486</v>
       </c>
       <c r="H13" t="n">
-        <v>970.45</v>
+        <v>1000.4</v>
       </c>
       <c r="I13" t="n">
         <v>996.108581975377</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.29</v>
+        <v>-7.51</v>
       </c>
       <c r="L13" t="n">
-        <v>8.109999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="M13" t="n">
         <v>3.19</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.25</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42492</v>
+        <v>42493</v>
       </c>
       <c r="H14" t="n">
-        <v>952.5</v>
+        <v>942.4299999999999</v>
       </c>
       <c r="I14" t="n">
         <v>942.6705359088805</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.79</v>
+        <v>-5.79</v>
       </c>
       <c r="L14" t="n">
         <v>6.89</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.22</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42698</v>
+        <v>42699</v>
       </c>
       <c r="H15" t="n">
-        <v>579</v>
+        <v>621.63</v>
       </c>
       <c r="I15" t="n">
         <v>589.4894306454704</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K15" t="n">
-        <v>38.56</v>
+        <v>34.04</v>
       </c>
       <c r="L15" t="n">
         <v>3.02</v>
@@ -1296,7 +1475,7 @@
         <v>2.24</v>
       </c>
       <c r="N15" t="n">
-        <v>6.41</v>
+        <v>7.36</v>
       </c>
       <c r="O15" t="n">
         <v>-1.06</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>18.54</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42726</v>
+        <v>42727</v>
       </c>
       <c r="H16" t="n">
-        <v>679.1799999999999</v>
+        <v>661.6799999999999</v>
       </c>
       <c r="I16" t="n">
         <v>665.5888241250439</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K16" t="n">
-        <v>9.26</v>
+        <v>6.44</v>
       </c>
       <c r="L16" t="n">
         <v>8.199999999999999</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>10.95</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42752</v>
+        <v>42753</v>
       </c>
       <c r="H17" t="n">
-        <v>711.55</v>
+        <v>757.48</v>
       </c>
       <c r="I17" t="n">
         <v>717.6775289772155</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.54</v>
+        <v>-14.48</v>
       </c>
       <c r="L17" t="n">
-        <v>10.25</v>
+        <v>14.99</v>
       </c>
       <c r="M17" t="n">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.56</v>
+        <v>6.45</v>
       </c>
       <c r="O17" t="n">
         <v>-2.58</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.92</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H18" t="n">
-        <v>764.03</v>
+        <v>727.7</v>
       </c>
       <c r="I18" t="n">
         <v>735.8766170921803</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K18" t="n">
-        <v>0.86</v>
+        <v>-3.93</v>
       </c>
       <c r="L18" t="n">
         <v>7.98</v>
@@ -1467,7 +1682,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>3.09</v>
+        <v>4.76</v>
       </c>
       <c r="O18" t="n">
         <v>6.45</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>10.64</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42888</v>
+        <v>42891</v>
       </c>
       <c r="H19" t="n">
-        <v>678.1</v>
+        <v>746.1</v>
       </c>
       <c r="I19" t="n">
         <v>731.1560681229776</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>6.82</v>
+        <v>-2.53</v>
       </c>
       <c r="L19" t="n">
         <v>5.37</v>
@@ -1524,7 +1751,7 @@
         <v>0.83</v>
       </c>
       <c r="N19" t="n">
-        <v>2.87</v>
+        <v>10.03</v>
       </c>
       <c r="O19" t="n">
         <v>-4.76</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>15.67</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42957</v>
+        <v>42958</v>
       </c>
       <c r="H20" t="n">
-        <v>813.53</v>
+        <v>802.55</v>
       </c>
       <c r="I20" t="n">
         <v>809.5794304604021</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K20" t="n">
-        <v>9.039999999999999</v>
+        <v>7.57</v>
       </c>
       <c r="L20" t="n">
         <v>9.43</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.07</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42983</v>
+        <v>42984</v>
       </c>
       <c r="H21" t="n">
-        <v>873.6</v>
+        <v>875.8</v>
       </c>
       <c r="I21" t="n">
         <v>875.3401576737494</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.85</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L21" t="n">
         <v>10.27</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>7.84</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42999</v>
+        <v>43000</v>
       </c>
       <c r="H22" t="n">
-        <v>872.1</v>
+        <v>847.3</v>
       </c>
       <c r="I22" t="n">
         <v>853.4328226199297</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.42</v>
+        <v>-3.25</v>
       </c>
       <c r="L22" t="n">
-        <v>1.66</v>
+        <v>3.97</v>
       </c>
       <c r="M22" t="n">
         <v>0.93</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>2.84</v>
       </c>
       <c r="O22" t="n">
         <v>0.25</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.74</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43046</v>
+        <v>43047</v>
       </c>
       <c r="H23" t="n">
-        <v>871.45</v>
+        <v>884.2</v>
       </c>
       <c r="I23" t="n">
         <v>876.1733559029307</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.85</v>
+        <v>-4.36</v>
       </c>
       <c r="L23" t="n">
-        <v>5.58</v>
+        <v>7.73</v>
       </c>
       <c r="M23" t="n">
         <v>1.32</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>8.01</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H24" t="n">
-        <v>1024.6</v>
+        <v>993.05</v>
       </c>
       <c r="I24" t="n">
         <v>997.4663658354818</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K24" t="n">
-        <v>15.88</v>
+        <v>12.31</v>
       </c>
       <c r="L24" t="n">
         <v>2.42</v>
       </c>
       <c r="M24" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="N24" t="n">
         <v>3.32</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>14.21</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43201</v>
+        <v>43202</v>
       </c>
       <c r="H25" t="n">
-        <v>1042.6</v>
+        <v>1069.9</v>
       </c>
       <c r="I25" t="n">
         <v>1061.666990848286</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.99</v>
+        <v>-7.74</v>
       </c>
       <c r="L25" t="n">
-        <v>7.55</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>1.86</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43348</v>
+        <v>43349</v>
       </c>
       <c r="H26" t="n">
-        <v>1380.7</v>
+        <v>1352.5</v>
       </c>
       <c r="I26" t="n">
         <v>1354.775269351762</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K26" t="n">
-        <v>29.05</v>
+        <v>26.41</v>
       </c>
       <c r="L26" t="n">
         <v>2.7</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.31</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43529</v>
+        <v>43530</v>
       </c>
       <c r="H27" t="n">
-        <v>926.05</v>
+        <v>950.1</v>
       </c>
       <c r="I27" t="n">
         <v>926.3015031687264</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K27" t="n">
-        <v>31.53</v>
+        <v>29.75</v>
       </c>
       <c r="L27" t="n">
         <v>1.99</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>7</v>
+      </c>
+      <c r="U27" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>8.69</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43578</v>
+        <v>43579</v>
       </c>
       <c r="H28" t="n">
-        <v>950.6</v>
+        <v>929.75</v>
       </c>
       <c r="I28" t="n">
         <v>930.5870595840315</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K28" t="n">
-        <v>0.05</v>
+        <v>-2.14</v>
       </c>
       <c r="L28" t="n">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="M28" t="n">
         <v>0.37</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>8.33</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43647</v>
+        <v>43648</v>
       </c>
       <c r="H29" t="n">
-        <v>898.9</v>
+        <v>920.8</v>
       </c>
       <c r="I29" t="n">
         <v>899.5270613201037</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K29" t="n">
-        <v>3.32</v>
+        <v>0.96</v>
       </c>
       <c r="L29" t="n">
         <v>3.02</v>
@@ -2094,7 +2441,7 @@
         <v>1.29</v>
       </c>
       <c r="N29" t="n">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="O29" t="n">
         <v>-2.19</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>7.13</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H30" t="n">
-        <v>889.85</v>
+        <v>856.9</v>
       </c>
       <c r="I30" t="n">
         <v>863.3567583758999</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.36</v>
+        <v>-6.94</v>
       </c>
       <c r="L30" t="n">
-        <v>3.81</v>
+        <v>7.85</v>
       </c>
       <c r="M30" t="n">
-        <v>0.03</v>
+        <v>2.67</v>
       </c>
       <c r="N30" t="n">
-        <v>2.68</v>
+        <v>3.7</v>
       </c>
       <c r="O30" t="n">
         <v>2.44</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.01</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43731</v>
+        <v>43732</v>
       </c>
       <c r="H31" t="n">
-        <v>649.2</v>
+        <v>685.5</v>
       </c>
       <c r="I31" t="n">
         <v>680.6020392100635</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K31" t="n">
-        <v>24.24</v>
+        <v>20</v>
       </c>
       <c r="L31" t="n">
         <v>1.52</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>13.38</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43886</v>
+        <v>43887</v>
       </c>
       <c r="H32" t="n">
-        <v>989.25</v>
+        <v>961.6</v>
       </c>
       <c r="I32" t="n">
         <v>966.5432072894074</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K32" t="n">
-        <v>44.31</v>
+        <v>40.28</v>
       </c>
       <c r="L32" t="n">
         <v>11.01</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>14.14</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43892</v>
+        <v>43893</v>
       </c>
       <c r="H33" t="n">
-        <v>941.25</v>
+        <v>1037.85</v>
       </c>
       <c r="I33" t="n">
         <v>1023.530486804076</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
-        <v>2.12</v>
+        <v>-7.93</v>
       </c>
       <c r="L33" t="n">
-        <v>3.27</v>
+        <v>11.4</v>
       </c>
       <c r="M33" t="n">
-        <v>0.48</v>
+        <v>2.23</v>
       </c>
       <c r="N33" t="n">
-        <v>6.63</v>
+        <v>10.26</v>
       </c>
       <c r="O33" t="n">
         <v>-2.8</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>19.65</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43903</v>
+        <v>43906</v>
       </c>
       <c r="H34" t="n">
-        <v>846.9</v>
+        <v>770.7</v>
       </c>
       <c r="I34" t="n">
         <v>833.8735556886984</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K34" t="n">
-        <v>-18.4</v>
+        <v>-25.74</v>
       </c>
       <c r="L34" t="n">
         <v>32.3</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>34.68</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43945</v>
+        <v>43948</v>
       </c>
       <c r="H35" t="n">
-        <v>751.25</v>
+        <v>829.15</v>
       </c>
       <c r="I35" t="n">
         <v>781.5615868123365</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K35" t="n">
-        <v>2.52</v>
+        <v>-7.58</v>
       </c>
       <c r="L35" t="n">
-        <v>7.02</v>
+        <v>11.59</v>
       </c>
       <c r="M35" t="n">
         <v>4.78</v>
       </c>
       <c r="N35" t="n">
-        <v>9.73</v>
+        <v>10.37</v>
       </c>
       <c r="O35" t="n">
         <v>-9</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>21.78</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H36" t="n">
-        <v>1524.1</v>
+        <v>1464.6</v>
       </c>
       <c r="I36" t="n">
         <v>1480.723974839007</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K36" t="n">
-        <v>83.81</v>
+        <v>76.64</v>
       </c>
       <c r="L36" t="n">
         <v>10.74</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>138</v>
+        <v>139</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>8</v>
+      </c>
+      <c r="U36" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>15.62</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44166</v>
+        <v>44167</v>
       </c>
       <c r="H37" t="n">
-        <v>1628.6</v>
+        <v>1684.3</v>
       </c>
       <c r="I37" t="n">
         <v>1665.086591746879</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K37" t="n">
-        <v>-11.2</v>
+        <v>-15</v>
       </c>
       <c r="L37" t="n">
-        <v>11.87</v>
+        <v>15.87</v>
       </c>
       <c r="M37" t="n">
         <v>1.5</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.32</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H38" t="n">
-        <v>6390.75</v>
+        <v>6029.8</v>
       </c>
       <c r="I38" t="n">
         <v>6072.786022625368</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K38" t="n">
-        <v>279.43</v>
+        <v>258</v>
       </c>
       <c r="L38" t="n">
         <v>12.84</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>239</v>
+        <v>240</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>12</v>
+      </c>
+      <c r="U38" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>14.19</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44572</v>
+        <v>44573</v>
       </c>
       <c r="H39" t="n">
-        <v>5938.75</v>
+        <v>6114.1</v>
       </c>
       <c r="I39" t="n">
         <v>6011.424955914918</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K39" t="n">
-        <v>1.51</v>
+        <v>-1.4</v>
       </c>
       <c r="L39" t="n">
         <v>6.37</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.91</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44613</v>
+        <v>44614</v>
       </c>
       <c r="H40" t="n">
-        <v>6733</v>
+        <v>6560.85</v>
       </c>
       <c r="I40" t="n">
         <v>6717.300879777625</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K40" t="n">
-        <v>10.12</v>
+        <v>7.31</v>
       </c>
       <c r="L40" t="n">
         <v>2.68</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>13.85</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44635</v>
+        <v>44636</v>
       </c>
       <c r="H41" t="n">
-        <v>6997.45</v>
+        <v>7213.4</v>
       </c>
       <c r="I41" t="n">
         <v>7196.806746896845</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.65</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L41" t="n">
         <v>11.11</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.49</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44669</v>
+        <v>44670</v>
       </c>
       <c r="H42" t="n">
-        <v>7815.95</v>
+        <v>7693.15</v>
       </c>
       <c r="I42" t="n">
         <v>7730.102588549505</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K42" t="n">
-        <v>8.35</v>
+        <v>6.65</v>
       </c>
       <c r="L42" t="n">
         <v>1.92</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>17.02</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44694</v>
+        <v>44697</v>
       </c>
       <c r="H43" t="n">
-        <v>7886.65</v>
+        <v>8121.15</v>
       </c>
       <c r="I43" t="n">
         <v>7901.286105856185</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.52</v>
+        <v>-5.56</v>
       </c>
       <c r="L43" t="n">
         <v>10.23</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>17.31</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44729</v>
+        <v>44732</v>
       </c>
       <c r="H44" t="n">
-        <v>7812.85</v>
+        <v>7254.85</v>
       </c>
       <c r="I44" t="n">
         <v>7662.057924924946</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.8</v>
+        <v>-10.67</v>
       </c>
       <c r="L44" t="n">
-        <v>5.43</v>
+        <v>11.34</v>
       </c>
       <c r="M44" t="n">
         <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>3.98</v>
+        <v>7.14</v>
       </c>
       <c r="O44" t="n">
         <v>2.97</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>18.5</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44764</v>
+        <v>44767</v>
       </c>
       <c r="H45" t="n">
-        <v>8386.299999999999</v>
+        <v>8529.4</v>
       </c>
       <c r="I45" t="n">
         <v>8486.053003947965</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K45" t="n">
-        <v>-15.6</v>
+        <v>-17.57</v>
       </c>
       <c r="L45" t="n">
-        <v>16.68</v>
+        <v>17.85</v>
       </c>
       <c r="M45" t="n">
         <v>1.87</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44795</v>
+        <v>44796</v>
       </c>
       <c r="H46" t="n">
-        <v>9788.700000000001</v>
+        <v>9618.75</v>
       </c>
       <c r="I46" t="n">
         <v>9732.418446444273</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K46" t="n">
-        <v>14.76</v>
+        <v>12.77</v>
       </c>
       <c r="L46" t="n">
         <v>2.66</v>
       </c>
       <c r="M46" t="n">
-        <v>0.39</v>
+        <v>2.23</v>
       </c>
       <c r="N46" t="n">
         <v>4.48</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11.91</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44921</v>
+        <v>44922</v>
       </c>
       <c r="H47" t="n">
-        <v>6252.65</v>
+        <v>6431.65</v>
       </c>
       <c r="I47" t="n">
         <v>6367.808732004276</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K47" t="n">
-        <v>35</v>
+        <v>33.13</v>
       </c>
       <c r="L47" t="n">
         <v>3.81</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44984</v>
+        <v>44985</v>
       </c>
       <c r="H48" t="n">
-        <v>6358.7</v>
+        <v>6129.25</v>
       </c>
       <c r="I48" t="n">
         <v>6310.857834991422</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.13</v>
+        <v>-4.7</v>
       </c>
       <c r="L48" t="n">
-        <v>4.66</v>
+        <v>5.33</v>
       </c>
       <c r="M48" t="n">
         <v>1.04</v>
       </c>
       <c r="N48" t="n">
-        <v>2.37</v>
+        <v>3.61</v>
       </c>
       <c r="O48" t="n">
         <v>2.86</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45026</v>
+        <v>45027</v>
       </c>
       <c r="H49" t="n">
-        <v>6201.1</v>
+        <v>6381.3</v>
       </c>
       <c r="I49" t="n">
         <v>6305.763500003253</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.17</v>
+        <v>-4.11</v>
       </c>
       <c r="L49" t="n">
-        <v>4.25</v>
+        <v>4.66</v>
       </c>
       <c r="M49" t="n">
         <v>1.86</v>
       </c>
       <c r="N49" t="n">
-        <v>2.19</v>
+        <v>2.91</v>
       </c>
       <c r="O49" t="n">
         <v>-3.61</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.55</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45127</v>
+        <v>45128</v>
       </c>
       <c r="H50" t="n">
-        <v>7494.3</v>
+        <v>7310.85</v>
       </c>
       <c r="I50" t="n">
         <v>7401.094671500178</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K50" t="n">
-        <v>17.44</v>
+        <v>14.57</v>
       </c>
       <c r="L50" t="n">
         <v>3.15</v>
@@ -3291,7 +3890,7 @@
         <v>4.85</v>
       </c>
       <c r="N50" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="O50" t="n">
         <v>2.91</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.16</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45163</v>
+        <v>45166</v>
       </c>
       <c r="H51" t="n">
-        <v>7301.45</v>
+        <v>7374.15</v>
       </c>
       <c r="I51" t="n">
         <v>7307.831473603478</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K51" t="n">
-        <v>0.13</v>
+        <v>-0.87</v>
       </c>
       <c r="L51" t="n">
         <v>1.9</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>4.66</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45308</v>
+        <v>45309</v>
       </c>
       <c r="H52" t="n">
-        <v>8597.799999999999</v>
+        <v>8310.700000000001</v>
       </c>
       <c r="I52" t="n">
         <v>8477.617379364465</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K52" t="n">
-        <v>16.59</v>
+        <v>12.7</v>
       </c>
       <c r="L52" t="n">
         <v>4.35</v>
@@ -3405,7 +4028,7 @@
         <v>1.41</v>
       </c>
       <c r="N52" t="n">
-        <v>3.29</v>
+        <v>3.34</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>6</v>
+      </c>
+      <c r="U52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.38</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="H53" t="n">
-        <v>7701.75</v>
+        <v>7997.9</v>
       </c>
       <c r="I53" t="n">
         <v>7960.505656750457</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K53" t="n">
-        <v>7.33</v>
+        <v>3.76</v>
       </c>
       <c r="L53" t="n">
         <v>3.61</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="H54" t="n">
-        <v>7493.35</v>
+        <v>7451</v>
       </c>
       <c r="I54" t="n">
         <v>7459.347790659927</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>-6.31</v>
+        <v>-6.84</v>
       </c>
       <c r="L54" t="n">
-        <v>6.51</v>
+        <v>7.88</v>
       </c>
       <c r="M54" t="n">
         <v>1.08</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>6.94</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45527</v>
+        <v>45530</v>
       </c>
       <c r="H55" t="n">
-        <v>7088.15</v>
+        <v>7683.05</v>
       </c>
       <c r="I55" t="n">
         <v>7109.719180624093</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K55" t="n">
-        <v>4.87</v>
+        <v>-3.11</v>
       </c>
       <c r="L55" t="n">
-        <v>1.67</v>
+        <v>6.56</v>
       </c>
       <c r="M55" t="n">
         <v>2.93</v>
       </c>
       <c r="N55" t="n">
-        <v>2.84</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="O55" t="n">
         <v>-0.57</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>5</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.84</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H56" t="n">
-        <v>7576.1</v>
+        <v>7430.65</v>
       </c>
       <c r="I56" t="n">
         <v>7460.976314671223</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.39</v>
+        <v>-3.29</v>
       </c>
       <c r="L56" t="n">
         <v>7.55</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.68</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45630</v>
+        <v>45631</v>
       </c>
       <c r="H57" t="n">
-        <v>7138.95</v>
+        <v>7367.75</v>
       </c>
       <c r="I57" t="n">
         <v>7149.955796046815</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K57" t="n">
-        <v>3.93</v>
+        <v>0.85</v>
       </c>
       <c r="L57" t="n">
         <v>8.029999999999999</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="H58" t="n">
-        <v>6925.55</v>
+        <v>6796.55</v>
       </c>
       <c r="I58" t="n">
         <v>6844.911288454777</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K58" t="n">
-        <v>-6</v>
+        <v>-7.75</v>
       </c>
       <c r="L58" t="n">
-        <v>8.19</v>
+        <v>8.74</v>
       </c>
       <c r="M58" t="n">
         <v>1.11</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>8.73</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45768</v>
+        <v>45769</v>
       </c>
       <c r="H59" t="n">
-        <v>5342</v>
+        <v>5480</v>
       </c>
       <c r="I59" t="n">
         <v>5387.394241471102</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K59" t="n">
-        <v>21.4</v>
+        <v>19.37</v>
       </c>
       <c r="L59" t="n">
         <v>1.9</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>13.91</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H60" t="n">
-        <v>6449.5</v>
+        <v>6220</v>
       </c>
       <c r="I60" t="n">
         <v>6321.83864206869</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K60" t="n">
-        <v>17.69</v>
+        <v>13.5</v>
       </c>
       <c r="L60" t="n">
         <v>3.86</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.26</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45852</v>
+        <v>45853</v>
       </c>
       <c r="H61" t="n">
-        <v>6179</v>
+        <v>6380</v>
       </c>
       <c r="I61" t="n">
         <v>6339.548127670952</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K61" t="n">
-        <v>0.66</v>
+        <v>-2.57</v>
       </c>
       <c r="L61" t="n">
         <v>4.29</v>
@@ -3918,7 +4649,7 @@
         <v>1.54</v>
       </c>
       <c r="N61" t="n">
-        <v>1.86</v>
+        <v>3.25</v>
       </c>
       <c r="O61" t="n">
         <v>-3.56</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>9.15</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45874</v>
+        <v>45875</v>
       </c>
       <c r="H62" t="n">
-        <v>5961.5</v>
+        <v>5816</v>
       </c>
       <c r="I62" t="n">
         <v>5868.898164927876</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K62" t="n">
-        <v>-6.56</v>
+        <v>-8.84</v>
       </c>
       <c r="L62" t="n">
-        <v>6.87</v>
+        <v>9.09</v>
       </c>
       <c r="M62" t="n">
         <v>0.54</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>7.86</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="H63" t="n">
-        <v>5553.5</v>
+        <v>5843.5</v>
       </c>
       <c r="I63" t="n">
         <v>5666.985620941122</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K63" t="n">
-        <v>4.51</v>
+        <v>-0.47</v>
       </c>
       <c r="L63" t="n">
         <v>2.68</v>
@@ -4032,7 +4787,7 @@
         <v>0.84</v>
       </c>
       <c r="N63" t="n">
-        <v>2.35</v>
+        <v>5.22</v>
       </c>
       <c r="O63" t="n">
         <v>-2.44</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>9.51</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H64" t="n">
-        <v>5461.5</v>
+        <v>5303</v>
       </c>
       <c r="I64" t="n">
         <v>5373.301937462022</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K64" t="n">
-        <v>-6.54</v>
+        <v>-9.25</v>
       </c>
       <c r="L64" t="n">
-        <v>7.08</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="M64" t="n">
         <v>0.4</v>
       </c>
       <c r="N64" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="O64" t="n">
         <v>5.22</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="H65" t="n">
-        <v>5544</v>
+        <v>5585.5</v>
       </c>
       <c r="I65" t="n">
         <v>5578.587687250037</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.54</v>
+        <v>-5.33</v>
       </c>
       <c r="L65" t="n">
-        <v>6.02</v>
+        <v>6.07</v>
       </c>
       <c r="M65" t="n">
         <v>0.88</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>6.67</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="H66" t="n">
-        <v>5242.5</v>
+        <v>5180</v>
       </c>
       <c r="I66" t="n">
         <v>5215.781643948409</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K66" t="n">
-        <v>-6.14</v>
+        <v>-7.26</v>
       </c>
       <c r="L66" t="n">
-        <v>6.53</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M66" t="n">
-        <v>0.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N66" t="n">
         <v>2.57</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>6.28</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="H67" t="n">
-        <v>5013.5</v>
+        <v>5413.5</v>
       </c>
       <c r="I67" t="n">
         <v>5268.726322536072</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K67" t="n">
-        <v>3.21</v>
+        <v>-4.51</v>
       </c>
       <c r="L67" t="n">
         <v>5.79</v>
       </c>
       <c r="M67" t="n">
-        <v>0.96</v>
+        <v>2.04</v>
       </c>
       <c r="N67" t="n">
-        <v>3.16</v>
+        <v>7.98</v>
       </c>
       <c r="O67" t="n">
         <v>-1.19</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>10.69</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="H68" t="n">
-        <v>5406</v>
+        <v>5198.5</v>
       </c>
       <c r="I68" t="n">
         <v>5266.396444067101</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.14</v>
+        <v>-3.97</v>
       </c>
       <c r="L68" t="n">
         <v>6.49</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>11.8</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H69" t="n">
-        <v>4411.4</v>
+        <v>4540.6</v>
       </c>
       <c r="I69" t="n">
         <v>4522.045173703194</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K69" t="n">
-        <v>15.14</v>
+        <v>12.66</v>
       </c>
       <c r="L69" t="n">
         <v>3.85</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>10.73</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="H70" t="n">
-        <v>4233.5</v>
+        <v>4193</v>
       </c>
       <c r="I70" t="n">
         <v>4209.973466218364</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K70" t="n">
-        <v>-6.76</v>
+        <v>-7.66</v>
       </c>
       <c r="L70" t="n">
-        <v>7.26</v>
+        <v>8.43</v>
       </c>
       <c r="M70" t="n">
         <v>1.31</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>12.33</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="H71" t="n">
-        <v>4327.2</v>
+        <v>4335.6</v>
       </c>
       <c r="I71" t="n">
         <v>4333.849202875865</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K71" t="n">
-        <v>-3.2</v>
+        <v>-3.4</v>
       </c>
       <c r="L71" t="n">
         <v>4.79</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>7.14</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H72" t="n">
-        <v>4092.2</v>
+        <v>4009.1</v>
       </c>
       <c r="I72" t="n">
         <v>4073.942682877363</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.61</v>
+        <v>-7.53</v>
       </c>
       <c r="L72" t="n">
-        <v>5.99</v>
+        <v>8.18</v>
       </c>
       <c r="M72" t="n">
         <v>1.22</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>9.41</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="H73" t="n">
-        <v>3672.9</v>
+        <v>3761.9</v>
       </c>
       <c r="I73" t="n">
         <v>3712.465502175173</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K73" t="n">
-        <v>8.390000000000001</v>
+        <v>6.17</v>
       </c>
       <c r="L73" t="n">
         <v>3.69</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>9.49</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="H74" t="n">
-        <v>3558</v>
+        <v>3497</v>
       </c>
       <c r="I74" t="n">
         <v>3530.453448983431</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.42</v>
+        <v>-7.04</v>
       </c>
       <c r="L74" t="n">
-        <v>6.3</v>
+        <v>7.63</v>
       </c>
       <c r="M74" t="n">
         <v>0.82</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>8.1</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="H75" t="n">
-        <v>3257</v>
+        <v>3426.7</v>
       </c>
       <c r="I75" t="n">
         <v>3326.835515509712</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K75" t="n">
-        <v>6.86</v>
+        <v>2.01</v>
       </c>
       <c r="L75" t="n">
         <v>1.46</v>
@@ -4716,7 +5615,7 @@
         <v>1.98</v>
       </c>
       <c r="N75" t="n">
-        <v>4.47</v>
+        <v>5.21</v>
       </c>
       <c r="O75" t="n">
         <v>-1.71</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4776,6 +5687,14 @@
       <c r="Q76" t="n">
         <v>11</v>
       </c>
+      <c r="R76" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9734,7 +10653,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.4</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -9744,7 +10663,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -9754,7 +10673,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8">
@@ -9764,7 +10683,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -9774,7 +10693,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67.5</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="10">
@@ -9784,7 +10703,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125.7</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="11">
@@ -9794,7 +10713,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -9804,7 +10723,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -9814,7 +10733,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36.5</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="14">
@@ -9824,7 +10743,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -9834,7 +10753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.61</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="16">
@@ -9844,7 +10763,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.79</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="17">
@@ -9854,7 +10773,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>279.43</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18">
@@ -9864,7 +10783,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.7</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="19">
@@ -9874,7 +10793,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.75</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="20">
@@ -9884,7 +10803,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.89</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="21">
@@ -9904,7 +10823,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -9914,7 +10833,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -9924,7 +10843,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="25">
@@ -9944,7 +10863,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.06</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="27">
@@ -9954,7 +10873,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14.56</v>
+        <v>17.84</v>
       </c>
     </row>
     <row r="28">
@@ -9964,7 +10883,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
